--- a/testdata/QuickDemoMetabolomicsData.xlsx
+++ b/testdata/QuickDemoMetabolomicsData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidbroadhurst/Github/QC-MXP/testdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dvdbrdhrst/GitHub/QC-MXP/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF5D5FC-6936-7F41-AE6E-F29ACCC24675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4995E14E-57BE-A341-83EC-A24E113BB58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,8 @@
     <sheet name="Data" sheetId="29" r:id="rId1"/>
     <sheet name="Peak" sheetId="28" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>

--- a/testdata/QuickDemoMetabolomicsData.xlsx
+++ b/testdata/QuickDemoMetabolomicsData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dvdbrdhrst/GitHub/QC-MXP/testdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidbroadhurst/Github/QC-MXP/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4995E14E-57BE-A341-83EC-A24E113BB58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E732A8F-90F0-3F45-B5A9-C0786448E4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,194 +556,194 @@
     <t>RT</t>
   </si>
   <si>
-    <t>mz:767.47558-rt:18.221</t>
-  </si>
-  <si>
-    <t>mz:289.84724-rt:0.675</t>
-  </si>
-  <si>
-    <t>mz:168.08715-rt:0.654</t>
-  </si>
-  <si>
-    <t>mz:376.24677-rt:15.803</t>
-  </si>
-  <si>
-    <t>mz:187.06052-rt:2.965</t>
-  </si>
-  <si>
-    <t>mz:274.16349-rt:0.753</t>
-  </si>
-  <si>
-    <t>mz:599.2863-rt:15.853</t>
-  </si>
-  <si>
-    <t>mz:614.45095-rt:16.765</t>
-  </si>
-  <si>
-    <t>mz:821.59128-rt:18.821</t>
-  </si>
-  <si>
-    <t>mz:598.43096-rt:15.867</t>
-  </si>
-  <si>
-    <t>mz:501.28454-rt:18.241</t>
-  </si>
-  <si>
-    <t>mz:624.51041-rt:17.199</t>
-  </si>
-  <si>
-    <t>mz:135.06828-rt:1.287</t>
-  </si>
-  <si>
-    <t>mz:853.56075-rt:18.076</t>
-  </si>
-  <si>
-    <t>mz:331.83383-rt:0.669</t>
-  </si>
-  <si>
-    <t>mz:174.1001-rt:0.759</t>
-  </si>
-  <si>
-    <t>mz:191.01662-rt:0.712</t>
-  </si>
-  <si>
-    <t>mz:780.58354-rt:18.821</t>
-  </si>
-  <si>
-    <t>mz:1012.63105-rt:15.859</t>
-  </si>
-  <si>
-    <t>mz:717.56585-rt:19.293</t>
-  </si>
-  <si>
-    <t>mz:206.16668-rt:16.464</t>
-  </si>
-  <si>
-    <t>mz:205.88626-rt:0.669</t>
-  </si>
-  <si>
-    <t>mz:1096.61246-rt:15.967</t>
-  </si>
-  <si>
-    <t>mz:809.5232-rt:0.669</t>
-  </si>
-  <si>
-    <t>mz:157.11001-rt:4.958</t>
-  </si>
-  <si>
-    <t>mz:160.12086-rt:0.689</t>
-  </si>
-  <si>
-    <t>mz:104.04752-rt:1.435</t>
-  </si>
-  <si>
-    <t>mz:1571.05136-rt:18.651</t>
-  </si>
-  <si>
-    <t>mz:407.76131-rt:0.675</t>
-  </si>
-  <si>
-    <t>mz:396.06295-rt:5.027</t>
-  </si>
-  <si>
-    <t>mz:829.55831-rt:18.52</t>
-  </si>
-  <si>
-    <t>mz:148.0109-rt:1.441</t>
-  </si>
-  <si>
-    <t>mz:749.53487-rt:18.255</t>
-  </si>
-  <si>
-    <t>mz:582.27941-rt:15.858</t>
-  </si>
-  <si>
-    <t>mz:757.56222-rt:18.618</t>
-  </si>
-  <si>
-    <t>mz:865.52734-rt:19.238</t>
-  </si>
-  <si>
-    <t>mz:105.04221-rt:0.707</t>
-  </si>
-  <si>
-    <t>mz:286.22945-rt:16.024</t>
-  </si>
-  <si>
-    <t>mz:809.58251-rt:18.683</t>
-  </si>
-  <si>
-    <t>mz:189.95607-rt:0.968</t>
-  </si>
-  <si>
-    <t>mz:274.62479-rt:15.858</t>
-  </si>
-  <si>
-    <t>mz:354.27639-rt:15.803</t>
-  </si>
-  <si>
-    <t>mz:677.49812-rt:18.106</t>
-  </si>
-  <si>
-    <t>mz:311.77512-rt:0.67</t>
-  </si>
-  <si>
-    <t>mz:198.16159-rt:16.99</t>
-  </si>
-  <si>
-    <t>mz:541.31331-rt:15.478</t>
-  </si>
-  <si>
-    <t>mz:1164.49332-rt:12.388</t>
-  </si>
-  <si>
-    <t>mz:265.63139-rt:15.178</t>
-  </si>
-  <si>
-    <t>mz:145.11023-rt:4.165</t>
-  </si>
-  <si>
-    <t>mz:543.33186-rt:15.255</t>
-  </si>
-  <si>
-    <t>mz:795.50689-rt:18.663</t>
-  </si>
-  <si>
-    <t>mz:1529.959-rt:15.862</t>
-  </si>
-  <si>
-    <t>mz:285.13603-rt:12.575</t>
-  </si>
-  <si>
-    <t>mz:312.26616-rt:17.135</t>
-  </si>
-  <si>
-    <t>mz:799.49446-rt:0.666</t>
-  </si>
-  <si>
-    <t>mz:783.56876-rt:18.999</t>
-  </si>
-  <si>
-    <t>mz:484.35193-rt:17.256</t>
-  </si>
-  <si>
-    <t>mz:281.27169-rt:16.245</t>
-  </si>
-  <si>
-    <t>mz:507.36796-rt:16.385</t>
-  </si>
-  <si>
-    <t>mz:279.81844-rt:0.673</t>
-  </si>
-  <si>
     <t>Reference</t>
+  </si>
+  <si>
+    <t>Metabolite 1</t>
+  </si>
+  <si>
+    <t>Metabolite 2</t>
+  </si>
+  <si>
+    <t>Metabolite 3</t>
+  </si>
+  <si>
+    <t>Metabolite 4</t>
+  </si>
+  <si>
+    <t>Metabolite 5</t>
+  </si>
+  <si>
+    <t>Metabolite 6</t>
+  </si>
+  <si>
+    <t>Metabolite 7</t>
+  </si>
+  <si>
+    <t>Metabolite 8</t>
+  </si>
+  <si>
+    <t>Metabolite 9</t>
+  </si>
+  <si>
+    <t>Metabolite 10</t>
+  </si>
+  <si>
+    <t>Metabolite 11</t>
+  </si>
+  <si>
+    <t>Metabolite 12</t>
+  </si>
+  <si>
+    <t>Metabolite 13</t>
+  </si>
+  <si>
+    <t>Metabolite 14</t>
+  </si>
+  <si>
+    <t>Metabolite 15</t>
+  </si>
+  <si>
+    <t>Metabolite 16</t>
+  </si>
+  <si>
+    <t>Metabolite 17</t>
+  </si>
+  <si>
+    <t>Metabolite 18</t>
+  </si>
+  <si>
+    <t>Metabolite 19</t>
+  </si>
+  <si>
+    <t>Metabolite 20</t>
+  </si>
+  <si>
+    <t>Metabolite 21</t>
+  </si>
+  <si>
+    <t>Metabolite 22</t>
+  </si>
+  <si>
+    <t>Metabolite 23</t>
+  </si>
+  <si>
+    <t>Metabolite 24</t>
+  </si>
+  <si>
+    <t>Metabolite 25</t>
+  </si>
+  <si>
+    <t>Metabolite 26</t>
+  </si>
+  <si>
+    <t>Metabolite 27</t>
+  </si>
+  <si>
+    <t>Metabolite 28</t>
+  </si>
+  <si>
+    <t>Metabolite 29</t>
+  </si>
+  <si>
+    <t>Metabolite 30</t>
+  </si>
+  <si>
+    <t>Metabolite 31</t>
+  </si>
+  <si>
+    <t>Metabolite 32</t>
+  </si>
+  <si>
+    <t>Metabolite 33</t>
+  </si>
+  <si>
+    <t>Metabolite 34</t>
+  </si>
+  <si>
+    <t>Metabolite 35</t>
+  </si>
+  <si>
+    <t>Metabolite 36</t>
+  </si>
+  <si>
+    <t>Metabolite 37</t>
+  </si>
+  <si>
+    <t>Metabolite 38</t>
+  </si>
+  <si>
+    <t>Metabolite 39</t>
+  </si>
+  <si>
+    <t>Metabolite 40</t>
+  </si>
+  <si>
+    <t>Metabolite 41</t>
+  </si>
+  <si>
+    <t>Metabolite 42</t>
+  </si>
+  <si>
+    <t>Metabolite 43</t>
+  </si>
+  <si>
+    <t>Metabolite 44</t>
+  </si>
+  <si>
+    <t>Metabolite 45</t>
+  </si>
+  <si>
+    <t>Metabolite 46</t>
+  </si>
+  <si>
+    <t>Metabolite 47</t>
+  </si>
+  <si>
+    <t>Metabolite 48</t>
+  </si>
+  <si>
+    <t>Metabolite 49</t>
+  </si>
+  <si>
+    <t>Metabolite 50</t>
+  </si>
+  <si>
+    <t>Metabolite 51</t>
+  </si>
+  <si>
+    <t>Metabolite 52</t>
+  </si>
+  <si>
+    <t>Metabolite 53</t>
+  </si>
+  <si>
+    <t>Metabolite 54</t>
+  </si>
+  <si>
+    <t>Metabolite 55</t>
+  </si>
+  <si>
+    <t>Metabolite 56</t>
+  </si>
+  <si>
+    <t>Metabolite 57</t>
+  </si>
+  <si>
+    <t>Metabolite 58</t>
+  </si>
+  <si>
+    <t>Metabolite 59</t>
+  </si>
+  <si>
+    <t>Metabolite 60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -770,6 +770,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3901,7 +3907,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -5853,7 +5859,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -7790,7 +7796,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -14016,7 +14022,7 @@
         <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -15953,7 +15959,7 @@
         <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -17857,7 +17863,7 @@
         <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -21519,6 +21525,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 ECU Internal Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -21559,7 +21568,7 @@
         <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="D2">
         <v>757.56222000000002</v>
@@ -21576,7 +21585,7 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="D3">
         <v>541.31331</v>
@@ -21593,7 +21602,7 @@
         <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D4">
         <v>780.58353999999997</v>
@@ -21610,7 +21619,7 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="D5">
         <v>105.04221</v>
@@ -21627,7 +21636,7 @@
         <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="D6">
         <v>543.33186000000001</v>
@@ -21644,7 +21653,7 @@
         <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="D7">
         <v>281.27168999999998</v>
@@ -21661,7 +21670,7 @@
         <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="D8">
         <v>285.13603000000001</v>
@@ -21678,7 +21687,7 @@
         <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="D9">
         <v>749.53486999999996</v>
@@ -21695,7 +21704,7 @@
         <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="D10">
         <v>354.27638999999999</v>
@@ -21712,7 +21721,7 @@
         <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D11">
         <v>205.88625999999999</v>
@@ -21729,7 +21738,7 @@
         <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="D12">
         <v>104.04752000000001</v>
@@ -21746,7 +21755,7 @@
         <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="D13">
         <v>286.22944999999999</v>
@@ -21763,7 +21772,7 @@
         <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D14">
         <v>135.06827999999999</v>
@@ -21780,7 +21789,7 @@
         <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D15">
         <v>614.45095000000003</v>
@@ -21797,7 +21806,7 @@
         <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D16">
         <v>168.08715000000001</v>
@@ -21814,7 +21823,7 @@
         <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="D17">
         <v>311.77512000000002</v>
@@ -21831,7 +21840,7 @@
         <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D18">
         <v>312.26616000000001</v>
@@ -21848,7 +21857,7 @@
         <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="D19">
         <v>795.50689</v>
@@ -21865,7 +21874,7 @@
         <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="D20">
         <v>507.36795999999998</v>
@@ -21882,7 +21891,7 @@
         <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="D21">
         <v>198.16158999999999</v>
@@ -21899,7 +21908,7 @@
         <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="D22">
         <v>783.56876</v>
@@ -21933,7 +21942,7 @@
         <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="D24">
         <v>1164.49332</v>
@@ -21950,7 +21959,7 @@
         <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D25">
         <v>274.62479000000002</v>
@@ -21967,7 +21976,7 @@
         <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D26">
         <v>148.01089999999999</v>
@@ -21984,7 +21993,7 @@
         <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D27">
         <v>189.95607000000001</v>
@@ -22001,7 +22010,7 @@
         <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D28">
         <v>187.06052</v>
@@ -22018,7 +22027,7 @@
         <v>141</v>
       </c>
       <c r="C29" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D29">
         <v>599.28629999999998</v>
@@ -22035,7 +22044,7 @@
         <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D30">
         <v>677.49811999999997</v>
@@ -22069,7 +22078,7 @@
         <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="D32">
         <v>717.56584999999995</v>
@@ -22086,7 +22095,7 @@
         <v>145</v>
       </c>
       <c r="C33" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="D33">
         <v>1529.9590000000001</v>
@@ -22103,7 +22112,7 @@
         <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D34">
         <v>265.63139000000001</v>
@@ -22120,7 +22129,7 @@
         <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D35">
         <v>160.12085999999999</v>
@@ -22137,7 +22146,7 @@
         <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="D36">
         <v>174.1001</v>
@@ -22154,7 +22163,7 @@
         <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D37">
         <v>1012.63105</v>
@@ -22171,7 +22180,7 @@
         <v>150</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D38">
         <v>274.16349000000002</v>
@@ -22188,7 +22197,7 @@
         <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D39">
         <v>1571.0513599999999</v>
@@ -22205,7 +22214,7 @@
         <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D40">
         <v>865.52733999999998</v>
@@ -22222,7 +22231,7 @@
         <v>153</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="D41">
         <v>331.83382999999998</v>
@@ -22239,7 +22248,7 @@
         <v>154</v>
       </c>
       <c r="C42" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D42">
         <v>809.58250999999996</v>
@@ -22256,7 +22265,7 @@
         <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="D43">
         <v>279.81844000000001</v>
@@ -22273,7 +22282,7 @@
         <v>156</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="D44">
         <v>853.56074999999998</v>
@@ -22290,7 +22299,7 @@
         <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D45">
         <v>484.35192999999998</v>
@@ -22307,7 +22316,7 @@
         <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="D46">
         <v>157.11000999999999</v>
@@ -22324,7 +22333,7 @@
         <v>159</v>
       </c>
       <c r="C47" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="D47">
         <v>624.51040999999998</v>
@@ -22341,7 +22350,7 @@
         <v>160</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="D48">
         <v>206.16668000000001</v>
@@ -22358,7 +22367,7 @@
         <v>161</v>
       </c>
       <c r="C49" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D49">
         <v>582.27940999999998</v>
@@ -22375,7 +22384,7 @@
         <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="D50">
         <v>821.59127999999998</v>
@@ -22392,7 +22401,7 @@
         <v>163</v>
       </c>
       <c r="C51" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="D51">
         <v>191.01661999999999</v>
@@ -22409,7 +22418,7 @@
         <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="D52">
         <v>376.24677000000003</v>
@@ -22426,7 +22435,7 @@
         <v>165</v>
       </c>
       <c r="C53" t="s">
-        <v>176</v>
+        <v>228</v>
       </c>
       <c r="D53">
         <v>767.47558000000004</v>
@@ -22443,7 +22452,7 @@
         <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="D54">
         <v>501.28453999999999</v>
@@ -22477,7 +22486,7 @@
         <v>168</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="D56">
         <v>289.84724</v>
@@ -22494,7 +22503,7 @@
         <v>169</v>
       </c>
       <c r="C57" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="D57">
         <v>407.76130999999998</v>
@@ -22511,7 +22520,7 @@
         <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D58">
         <v>145.11023</v>
@@ -22528,7 +22537,7 @@
         <v>171</v>
       </c>
       <c r="C59" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="D59">
         <v>809.52319999999997</v>
@@ -22545,7 +22554,7 @@
         <v>172</v>
       </c>
       <c r="C60" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="D60">
         <v>598.43096000000003</v>
@@ -22562,7 +22571,7 @@
         <v>173</v>
       </c>
       <c r="C61" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="D61">
         <v>396.06295</v>
@@ -22572,6 +22581,10 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 ECU Internal Information</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/testdata/QuickDemoMetabolomicsData.xlsx
+++ b/testdata/QuickDemoMetabolomicsData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidbroadhurst/Github/QC-MXP/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E732A8F-90F0-3F45-B5A9-C0786448E4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10DF3531-032D-BA49-9D74-BB8C32E9962D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,194 +556,194 @@
     <t>RT</t>
   </si>
   <si>
+    <t>mz:767.47558-rt:18.221</t>
+  </si>
+  <si>
+    <t>mz:289.84724-rt:0.675</t>
+  </si>
+  <si>
+    <t>mz:168.08715-rt:0.654</t>
+  </si>
+  <si>
+    <t>mz:376.24677-rt:15.803</t>
+  </si>
+  <si>
+    <t>mz:187.06052-rt:2.965</t>
+  </si>
+  <si>
+    <t>mz:274.16349-rt:0.753</t>
+  </si>
+  <si>
+    <t>mz:599.2863-rt:15.853</t>
+  </si>
+  <si>
+    <t>mz:614.45095-rt:16.765</t>
+  </si>
+  <si>
+    <t>mz:821.59128-rt:18.821</t>
+  </si>
+  <si>
+    <t>mz:598.43096-rt:15.867</t>
+  </si>
+  <si>
+    <t>mz:501.28454-rt:18.241</t>
+  </si>
+  <si>
+    <t>mz:624.51041-rt:17.199</t>
+  </si>
+  <si>
+    <t>mz:135.06828-rt:1.287</t>
+  </si>
+  <si>
+    <t>mz:853.56075-rt:18.076</t>
+  </si>
+  <si>
+    <t>mz:331.83383-rt:0.669</t>
+  </si>
+  <si>
+    <t>mz:174.1001-rt:0.759</t>
+  </si>
+  <si>
+    <t>mz:191.01662-rt:0.712</t>
+  </si>
+  <si>
+    <t>mz:780.58354-rt:18.821</t>
+  </si>
+  <si>
+    <t>mz:1012.63105-rt:15.859</t>
+  </si>
+  <si>
+    <t>mz:717.56585-rt:19.293</t>
+  </si>
+  <si>
+    <t>mz:206.16668-rt:16.464</t>
+  </si>
+  <si>
+    <t>mz:205.88626-rt:0.669</t>
+  </si>
+  <si>
+    <t>mz:1096.61246-rt:15.967</t>
+  </si>
+  <si>
+    <t>mz:809.5232-rt:0.669</t>
+  </si>
+  <si>
+    <t>mz:157.11001-rt:4.958</t>
+  </si>
+  <si>
+    <t>mz:160.12086-rt:0.689</t>
+  </si>
+  <si>
+    <t>mz:104.04752-rt:1.435</t>
+  </si>
+  <si>
+    <t>mz:1571.05136-rt:18.651</t>
+  </si>
+  <si>
+    <t>mz:407.76131-rt:0.675</t>
+  </si>
+  <si>
+    <t>mz:396.06295-rt:5.027</t>
+  </si>
+  <si>
+    <t>mz:829.55831-rt:18.52</t>
+  </si>
+  <si>
+    <t>mz:148.0109-rt:1.441</t>
+  </si>
+  <si>
+    <t>mz:749.53487-rt:18.255</t>
+  </si>
+  <si>
+    <t>mz:582.27941-rt:15.858</t>
+  </si>
+  <si>
+    <t>mz:757.56222-rt:18.618</t>
+  </si>
+  <si>
+    <t>mz:865.52734-rt:19.238</t>
+  </si>
+  <si>
+    <t>mz:105.04221-rt:0.707</t>
+  </si>
+  <si>
+    <t>mz:286.22945-rt:16.024</t>
+  </si>
+  <si>
+    <t>mz:809.58251-rt:18.683</t>
+  </si>
+  <si>
+    <t>mz:189.95607-rt:0.968</t>
+  </si>
+  <si>
+    <t>mz:274.62479-rt:15.858</t>
+  </si>
+  <si>
+    <t>mz:354.27639-rt:15.803</t>
+  </si>
+  <si>
+    <t>mz:677.49812-rt:18.106</t>
+  </si>
+  <si>
+    <t>mz:311.77512-rt:0.67</t>
+  </si>
+  <si>
+    <t>mz:198.16159-rt:16.99</t>
+  </si>
+  <si>
+    <t>mz:541.31331-rt:15.478</t>
+  </si>
+  <si>
+    <t>mz:1164.49332-rt:12.388</t>
+  </si>
+  <si>
+    <t>mz:265.63139-rt:15.178</t>
+  </si>
+  <si>
+    <t>mz:145.11023-rt:4.165</t>
+  </si>
+  <si>
+    <t>mz:543.33186-rt:15.255</t>
+  </si>
+  <si>
+    <t>mz:795.50689-rt:18.663</t>
+  </si>
+  <si>
+    <t>mz:1529.959-rt:15.862</t>
+  </si>
+  <si>
+    <t>mz:285.13603-rt:12.575</t>
+  </si>
+  <si>
+    <t>mz:312.26616-rt:17.135</t>
+  </si>
+  <si>
+    <t>mz:799.49446-rt:0.666</t>
+  </si>
+  <si>
+    <t>mz:783.56876-rt:18.999</t>
+  </si>
+  <si>
+    <t>mz:484.35193-rt:17.256</t>
+  </si>
+  <si>
+    <t>mz:281.27169-rt:16.245</t>
+  </si>
+  <si>
+    <t>mz:507.36796-rt:16.385</t>
+  </si>
+  <si>
+    <t>mz:279.81844-rt:0.673</t>
+  </si>
+  <si>
     <t>Reference</t>
-  </si>
-  <si>
-    <t>Metabolite 1</t>
-  </si>
-  <si>
-    <t>Metabolite 2</t>
-  </si>
-  <si>
-    <t>Metabolite 3</t>
-  </si>
-  <si>
-    <t>Metabolite 4</t>
-  </si>
-  <si>
-    <t>Metabolite 5</t>
-  </si>
-  <si>
-    <t>Metabolite 6</t>
-  </si>
-  <si>
-    <t>Metabolite 7</t>
-  </si>
-  <si>
-    <t>Metabolite 8</t>
-  </si>
-  <si>
-    <t>Metabolite 9</t>
-  </si>
-  <si>
-    <t>Metabolite 10</t>
-  </si>
-  <si>
-    <t>Metabolite 11</t>
-  </si>
-  <si>
-    <t>Metabolite 12</t>
-  </si>
-  <si>
-    <t>Metabolite 13</t>
-  </si>
-  <si>
-    <t>Metabolite 14</t>
-  </si>
-  <si>
-    <t>Metabolite 15</t>
-  </si>
-  <si>
-    <t>Metabolite 16</t>
-  </si>
-  <si>
-    <t>Metabolite 17</t>
-  </si>
-  <si>
-    <t>Metabolite 18</t>
-  </si>
-  <si>
-    <t>Metabolite 19</t>
-  </si>
-  <si>
-    <t>Metabolite 20</t>
-  </si>
-  <si>
-    <t>Metabolite 21</t>
-  </si>
-  <si>
-    <t>Metabolite 22</t>
-  </si>
-  <si>
-    <t>Metabolite 23</t>
-  </si>
-  <si>
-    <t>Metabolite 24</t>
-  </si>
-  <si>
-    <t>Metabolite 25</t>
-  </si>
-  <si>
-    <t>Metabolite 26</t>
-  </si>
-  <si>
-    <t>Metabolite 27</t>
-  </si>
-  <si>
-    <t>Metabolite 28</t>
-  </si>
-  <si>
-    <t>Metabolite 29</t>
-  </si>
-  <si>
-    <t>Metabolite 30</t>
-  </si>
-  <si>
-    <t>Metabolite 31</t>
-  </si>
-  <si>
-    <t>Metabolite 32</t>
-  </si>
-  <si>
-    <t>Metabolite 33</t>
-  </si>
-  <si>
-    <t>Metabolite 34</t>
-  </si>
-  <si>
-    <t>Metabolite 35</t>
-  </si>
-  <si>
-    <t>Metabolite 36</t>
-  </si>
-  <si>
-    <t>Metabolite 37</t>
-  </si>
-  <si>
-    <t>Metabolite 38</t>
-  </si>
-  <si>
-    <t>Metabolite 39</t>
-  </si>
-  <si>
-    <t>Metabolite 40</t>
-  </si>
-  <si>
-    <t>Metabolite 41</t>
-  </si>
-  <si>
-    <t>Metabolite 42</t>
-  </si>
-  <si>
-    <t>Metabolite 43</t>
-  </si>
-  <si>
-    <t>Metabolite 44</t>
-  </si>
-  <si>
-    <t>Metabolite 45</t>
-  </si>
-  <si>
-    <t>Metabolite 46</t>
-  </si>
-  <si>
-    <t>Metabolite 47</t>
-  </si>
-  <si>
-    <t>Metabolite 48</t>
-  </si>
-  <si>
-    <t>Metabolite 49</t>
-  </si>
-  <si>
-    <t>Metabolite 50</t>
-  </si>
-  <si>
-    <t>Metabolite 51</t>
-  </si>
-  <si>
-    <t>Metabolite 52</t>
-  </si>
-  <si>
-    <t>Metabolite 53</t>
-  </si>
-  <si>
-    <t>Metabolite 54</t>
-  </si>
-  <si>
-    <t>Metabolite 55</t>
-  </si>
-  <si>
-    <t>Metabolite 56</t>
-  </si>
-  <si>
-    <t>Metabolite 57</t>
-  </si>
-  <si>
-    <t>Metabolite 58</t>
-  </si>
-  <si>
-    <t>Metabolite 59</t>
-  </si>
-  <si>
-    <t>Metabolite 60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -770,12 +770,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3907,7 +3901,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -5859,7 +5853,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -7796,7 +7790,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -14022,7 +14016,7 @@
         <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -15959,7 +15953,7 @@
         <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -17863,7 +17857,7 @@
         <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -21568,7 +21562,7 @@
         <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="D2">
         <v>757.56222000000002</v>
@@ -21585,7 +21579,7 @@
         <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="D3">
         <v>541.31331</v>
@@ -21602,7 +21596,7 @@
         <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D4">
         <v>780.58353999999997</v>
@@ -21619,7 +21613,7 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="D5">
         <v>105.04221</v>
@@ -21636,7 +21630,7 @@
         <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="D6">
         <v>543.33186000000001</v>
@@ -21653,7 +21647,7 @@
         <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="D7">
         <v>281.27168999999998</v>
@@ -21670,7 +21664,7 @@
         <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="D8">
         <v>285.13603000000001</v>
@@ -21687,7 +21681,7 @@
         <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="D9">
         <v>749.53486999999996</v>
@@ -21704,7 +21698,7 @@
         <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="D10">
         <v>354.27638999999999</v>
@@ -21721,7 +21715,7 @@
         <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D11">
         <v>205.88625999999999</v>
@@ -21738,7 +21732,7 @@
         <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="D12">
         <v>104.04752000000001</v>
@@ -21755,7 +21749,7 @@
         <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="D13">
         <v>286.22944999999999</v>
@@ -21772,7 +21766,7 @@
         <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D14">
         <v>135.06827999999999</v>
@@ -21789,7 +21783,7 @@
         <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D15">
         <v>614.45095000000003</v>
@@ -21806,7 +21800,7 @@
         <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D16">
         <v>168.08715000000001</v>
@@ -21823,7 +21817,7 @@
         <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="D17">
         <v>311.77512000000002</v>
@@ -21840,7 +21834,7 @@
         <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D18">
         <v>312.26616000000001</v>
@@ -21857,7 +21851,7 @@
         <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D19">
         <v>795.50689</v>
@@ -21874,7 +21868,7 @@
         <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="D20">
         <v>507.36795999999998</v>
@@ -21891,7 +21885,7 @@
         <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="D21">
         <v>198.16158999999999</v>
@@ -21908,7 +21902,7 @@
         <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="D22">
         <v>783.56876</v>
@@ -21942,7 +21936,7 @@
         <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="D24">
         <v>1164.49332</v>
@@ -21959,7 +21953,7 @@
         <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="D25">
         <v>274.62479000000002</v>
@@ -21976,7 +21970,7 @@
         <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D26">
         <v>148.01089999999999</v>
@@ -21993,7 +21987,7 @@
         <v>139</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D27">
         <v>189.95607000000001</v>
@@ -22010,7 +22004,7 @@
         <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="D28">
         <v>187.06052</v>
@@ -22027,7 +22021,7 @@
         <v>141</v>
       </c>
       <c r="C29" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D29">
         <v>599.28629999999998</v>
@@ -22044,7 +22038,7 @@
         <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D30">
         <v>677.49811999999997</v>
@@ -22078,7 +22072,7 @@
         <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D32">
         <v>717.56584999999995</v>
@@ -22095,7 +22089,7 @@
         <v>145</v>
       </c>
       <c r="C33" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D33">
         <v>1529.9590000000001</v>
@@ -22112,7 +22106,7 @@
         <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D34">
         <v>265.63139000000001</v>
@@ -22129,7 +22123,7 @@
         <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D35">
         <v>160.12085999999999</v>
@@ -22146,7 +22140,7 @@
         <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="D36">
         <v>174.1001</v>
@@ -22163,7 +22157,7 @@
         <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D37">
         <v>1012.63105</v>
@@ -22180,7 +22174,7 @@
         <v>150</v>
       </c>
       <c r="C38" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="D38">
         <v>274.16349000000002</v>
@@ -22197,7 +22191,7 @@
         <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D39">
         <v>1571.0513599999999</v>
@@ -22214,7 +22208,7 @@
         <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D40">
         <v>865.52733999999998</v>
@@ -22231,7 +22225,7 @@
         <v>153</v>
       </c>
       <c r="C41" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="D41">
         <v>331.83382999999998</v>
@@ -22248,7 +22242,7 @@
         <v>154</v>
       </c>
       <c r="C42" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D42">
         <v>809.58250999999996</v>
@@ -22265,7 +22259,7 @@
         <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D43">
         <v>279.81844000000001</v>
@@ -22282,7 +22276,7 @@
         <v>156</v>
       </c>
       <c r="C44" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="D44">
         <v>853.56074999999998</v>
@@ -22299,7 +22293,7 @@
         <v>157</v>
       </c>
       <c r="C45" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D45">
         <v>484.35192999999998</v>
@@ -22316,7 +22310,7 @@
         <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="D46">
         <v>157.11000999999999</v>
@@ -22333,7 +22327,7 @@
         <v>159</v>
       </c>
       <c r="C47" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="D47">
         <v>624.51040999999998</v>
@@ -22350,7 +22344,7 @@
         <v>160</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="D48">
         <v>206.16668000000001</v>
@@ -22367,7 +22361,7 @@
         <v>161</v>
       </c>
       <c r="C49" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D49">
         <v>582.27940999999998</v>
@@ -22384,7 +22378,7 @@
         <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="D50">
         <v>821.59127999999998</v>
@@ -22401,7 +22395,7 @@
         <v>163</v>
       </c>
       <c r="C51" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="D51">
         <v>191.01661999999999</v>
@@ -22418,7 +22412,7 @@
         <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="D52">
         <v>376.24677000000003</v>
@@ -22435,7 +22429,7 @@
         <v>165</v>
       </c>
       <c r="C53" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="D53">
         <v>767.47558000000004</v>
@@ -22452,7 +22446,7 @@
         <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="D54">
         <v>501.28453999999999</v>
@@ -22486,7 +22480,7 @@
         <v>168</v>
       </c>
       <c r="C56" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="D56">
         <v>289.84724</v>
@@ -22503,7 +22497,7 @@
         <v>169</v>
       </c>
       <c r="C57" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="D57">
         <v>407.76130999999998</v>
@@ -22520,7 +22514,7 @@
         <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D58">
         <v>145.11023</v>
@@ -22537,7 +22531,7 @@
         <v>171</v>
       </c>
       <c r="C59" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="D59">
         <v>809.52319999999997</v>
@@ -22554,7 +22548,7 @@
         <v>172</v>
       </c>
       <c r="C60" t="s">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="D60">
         <v>598.43096000000003</v>
@@ -22571,7 +22565,7 @@
         <v>173</v>
       </c>
       <c r="C61" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="D61">
         <v>396.06295</v>
@@ -22581,7 +22575,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;K000000 ECU Internal Information</oddFooter>

--- a/testdata/QuickDemoMetabolomicsData.xlsx
+++ b/testdata/QuickDemoMetabolomicsData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidbroadhurst/Github/QC-MXP/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10DF3531-032D-BA49-9D74-BB8C32E9962D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF696F8F-0F4D-B14B-902B-C39E717279F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
